--- a/src/logic/sample_roulements.xlsx
+++ b/src/logic/sample_roulements.xlsx
@@ -122,6 +122,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -143,33 +144,39 @@
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -178,6 +185,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -185,12 +193,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -198,11 +208,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -210,12 +222,14 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -228,7 +242,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFCC"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFCCFF99"/>
       </patternFill>
     </fill>
     <fill>
@@ -239,14 +253,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99CC00"/>
-        <bgColor rgb="FFFFCC00"/>
+        <fgColor rgb="FFCCFF99"/>
+        <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF99"/>
-        <bgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFCCFF99"/>
       </patternFill>
     </fill>
   </fills>
@@ -375,232 +389,216 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -613,6 +611,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFCCFF99"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -730,32 +788,32 @@
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="21.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="21.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="4.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="7"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
       <c r="G2" s="8"/>
@@ -796,7 +854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
         <v>9</v>
       </c>
@@ -821,7 +879,7 @@
       <c r="H5" s="25"/>
       <c r="I5" s="11"/>
     </row>
-    <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
         <v>13</v>
       </c>
@@ -846,7 +904,7 @@
       <c r="H6" s="25"/>
       <c r="I6" s="11"/>
     </row>
-    <row r="7" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" s="1" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="28" t="s">
         <v>15</v>
       </c>
@@ -871,39 +929,39 @@
       <c r="H7" s="25"/>
       <c r="I7" s="11"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="31" t="s">
+    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="35"/>
+      <c r="B8" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="25"/>
       <c r="I8" s="11"/>
     </row>
-    <row r="9" s="7" customFormat="true" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="36"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="I9" s="40"/>
+    <row r="9" s="8" customFormat="true" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
@@ -940,7 +998,7 @@
       </c>
       <c r="H11" s="25"/>
     </row>
-    <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="20" t="s">
         <v>9</v>
       </c>
@@ -965,7 +1023,7 @@
       <c r="H12" s="25"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
         <v>13</v>
       </c>
@@ -990,7 +1048,7 @@
       <c r="H13" s="25"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="1" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
         <v>15</v>
       </c>
@@ -1015,50 +1073,50 @@
       <c r="H14" s="25"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="s">
+    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="35"/>
+      <c r="B15" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="25"/>
       <c r="I15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="41"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="37"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="13"/>
-      <c r="C17" s="42"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
@@ -1085,7 +1143,7 @@
       <c r="H18" s="25"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
         <v>9</v>
       </c>
@@ -1095,7 +1153,7 @@
       <c r="C19" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="43" t="s">
+      <c r="D19" s="39" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="22" t="s">
@@ -1110,7 +1168,7 @@
       <c r="H19" s="25"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
         <v>13</v>
       </c>
@@ -1129,13 +1187,13 @@
       <c r="F20" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="40" t="s">
         <v>12</v>
       </c>
       <c r="H20" s="25"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="1" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
         <v>15</v>
       </c>
@@ -1160,46 +1218,46 @@
       <c r="H21" s="25"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="31" t="s">
+    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="35"/>
+      <c r="B22" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="25"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" s="7" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="I23" s="41"/>
+    <row r="23" s="8" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="6"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="I23" s="37"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="13"/>
-      <c r="C24" s="46"/>
+      <c r="C24" s="42"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
@@ -1228,7 +1286,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="20" t="s">
         <v>9</v>
       </c>
@@ -1238,7 +1296,7 @@
       <c r="C26" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D26" s="43" t="s">
+      <c r="D26" s="39" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="22" t="s">
@@ -1253,7 +1311,7 @@
       <c r="H26" s="25"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="26" t="s">
         <v>13</v>
       </c>
@@ -1272,13 +1330,13 @@
       <c r="F27" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="44" t="s">
+      <c r="G27" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H27" s="25"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" s="30" customFormat="true" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="1" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
         <v>15</v>
       </c>
@@ -1303,29 +1361,29 @@
       <c r="H28" s="25"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="31" t="s">
+    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="35"/>
+      <c r="B29" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="25"/>
       <c r="I29" s="11"/>
     </row>
   </sheetData>
@@ -1386,100 +1444,100 @@
   <dimension ref="B1:F10"/>
   <sheetFormatPr defaultColWidth="11.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="64.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="1.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="5.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="64.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="1.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="15.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-    </row>
-    <row r="4" customFormat="false" ht="66" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="51" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+    </row>
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-    </row>
-    <row r="6" customFormat="false" ht="26.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="47" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="52" t="s">
+      <c r="C6" s="43"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="48" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-    </row>
-    <row r="8" customFormat="false" ht="40.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="53" t="s">
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="56" t="s">
+      <c r="C8" s="50"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="52" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
